--- a/SauceDemo/src/test/resources/TestData.xlsx
+++ b/SauceDemo/src/test/resources/TestData.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18300" windowHeight="3012"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
     <sheet name="Details" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
